--- a/erp-server/erp-server-file/src/main/resources/excel/wms/warehouseExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/warehouseExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="warehouse" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>金蝶仓库编号</t>
   </si>
@@ -80,6 +80,21 @@
     <t>创建时间</t>
   </si>
   <si>
+    <t>所属渠道</t>
+  </si>
+  <si>
+    <t>发货组织</t>
+  </si>
+  <si>
+    <t>财务组织</t>
+  </si>
+  <si>
+    <t>启用时间</t>
+  </si>
+  <si>
+    <t>停用时间</t>
+  </si>
+  <si>
     <t>{.kingdeeWarehouseCode}</t>
   </si>
   <si>
@@ -129,6 +144,21 @@
   </si>
   <si>
     <t>{.createTime}</t>
+  </si>
+  <si>
+    <t>{.channelAffiliationName}</t>
+  </si>
+  <si>
+    <t>{.shippingOrganizationName}</t>
+  </si>
+  <si>
+    <t>{.financialOrganizationName}</t>
+  </si>
+  <si>
+    <t>{.openTime}</t>
+  </si>
+  <si>
+    <t>{.closeTime}</t>
   </si>
 </sst>
 </file>
@@ -141,7 +171,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -154,13 +184,6 @@
       <sz val="13"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -637,151 +660,151 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -792,7 +815,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1328,7 +1351,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1342,9 +1365,13 @@
     <col min="14" max="15" width="20" customWidth="1"/>
     <col min="16" max="16" width="10" customWidth="1"/>
     <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="18" max="18" width="28.25" customWidth="1"/>
+    <col min="19" max="19" width="23.75" customWidth="1"/>
+    <col min="20" max="20" width="17" customWidth="1"/>
+    <col min="21" max="22" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:17">
+    <row r="1" ht="15" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1396,58 +1423,88 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:22">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/warehouseExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/warehouseExport.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>金蝶仓库编号</t>
   </si>
@@ -95,6 +95,9 @@
     <t>停用时间</t>
   </si>
   <si>
+    <t>国家</t>
+  </si>
+  <si>
     <t>{.kingdeeWarehouseCode}</t>
   </si>
   <si>
@@ -159,6 +162,9 @@
   </si>
   <si>
     <t>{.closeTime}</t>
+  </si>
+  <si>
+    <t>{.countryName}</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1357,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1368,10 +1374,10 @@
     <col min="18" max="18" width="28.25" customWidth="1"/>
     <col min="19" max="19" width="23.75" customWidth="1"/>
     <col min="20" max="20" width="17" customWidth="1"/>
-    <col min="21" max="22" width="14.875" customWidth="1"/>
+    <col min="21" max="23" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:22">
+    <row r="1" ht="15" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1438,73 +1444,79 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:23">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
